--- a/experiment/HAT+CNN_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/HAT+CNN_bestx4/Test/results-B100/B100.xlsx
@@ -455,7 +455,7 @@
         <v>24.08</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5733</v>
+        <v>0.5731000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         <v>28.74</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8132</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.57</v>
+        <v>26.56</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8134</v>
+        <v>0.8132</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>26.27</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7117</v>
+        <v>0.7115</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.9</v>
+        <v>33.87</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.8924</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.29</v>
+        <v>26.28</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7497</v>
+        <v>0.7499</v>
       </c>
     </row>
     <row r="9">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.52</v>
+        <v>27.53</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7886</v>
+        <v>0.7887</v>
       </c>
     </row>
     <row r="11">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.5</v>
+        <v>24.49</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7348</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         <v>28.1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7563</v>
+        <v>0.7566000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -611,7 +611,7 @@
         <v>30.04</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8089</v>
       </c>
     </row>
     <row r="15">
@@ -637,7 +637,7 @@
         <v>25.05</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6796</v>
+        <v>0.6794</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.86</v>
+        <v>24.87</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7611</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="18">
@@ -676,7 +676,7 @@
         <v>33.03</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8949</v>
+        <v>0.8947000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +689,7 @@
         <v>26.2</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7396</v>
+        <v>0.7398</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>26.08</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8036</v>
+        <v>0.8031</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.13</v>
+        <v>22.11</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6874</v>
+        <v>0.6864</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.91</v>
+        <v>23.92</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6317</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         <v>24.84</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5727</v>
+        <v>0.5728</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +754,7 @@
         <v>26.58</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7916</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>27.67</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8227</v>
+        <v>0.8226</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.01</v>
+        <v>27.03</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8389</v>
+        <v>0.8393</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.76</v>
+        <v>27.75</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7363</v>
+        <v>0.7359</v>
       </c>
     </row>
     <row r="29">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.71</v>
+        <v>32.68</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9035</v>
+        <v>0.9034</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         <v>19.89</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5064</v>
+        <v>0.5062</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         <v>29.8</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8171</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         <v>20.91</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4302</v>
+        <v>0.4308</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.21</v>
+        <v>25.22</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6726</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.49</v>
+        <v>24.48</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7585</v>
+        <v>0.7586000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35.01</v>
+        <v>34.99</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8939</v>
+        <v>0.8935999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         <v>27</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7416</v>
+        <v>0.7415</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         <v>27.91</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5128</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         <v>28.31</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7189</v>
+        <v>0.7188</v>
       </c>
     </row>
     <row r="40">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.14</v>
+        <v>36.13</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9573</v>
       </c>
     </row>
     <row r="42">
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.92</v>
+        <v>26.9</v>
       </c>
       <c r="C42" t="n">
         <v>0.7487</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.75</v>
+        <v>26.76</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7612</v>
+        <v>0.7614</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         <v>28.07</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8759</v>
+        <v>0.8757</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.8</v>
+        <v>24.79</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6845</v>
+        <v>0.6844</v>
       </c>
     </row>
     <row r="47">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.67</v>
+        <v>34.66</v>
       </c>
       <c r="C47" t="n">
         <v>0.8709</v>
@@ -1053,7 +1053,7 @@
         <v>22.79</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6262</v>
+        <v>0.6264999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24.99</v>
+        <v>24.98</v>
       </c>
       <c r="C49" t="n">
-        <v>0.636</v>
+        <v>0.6358</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.34</v>
+        <v>27.35</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8768</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="51">
@@ -1092,7 +1092,7 @@
         <v>32.22</v>
       </c>
       <c r="C51" t="n">
-        <v>0.841</v>
+        <v>0.8409</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.88</v>
+        <v>24.87</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6214</v>
+        <v>0.6208</v>
       </c>
     </row>
     <row r="53">
@@ -1118,7 +1118,7 @@
         <v>22.62</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7062</v>
+        <v>0.7066</v>
       </c>
     </row>
     <row r="54">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.66</v>
+        <v>32.67</v>
       </c>
       <c r="C54" t="n">
         <v>0.847</v>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.55</v>
+        <v>32.56</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8001</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.76</v>
+        <v>27.75</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.7784</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.68</v>
+        <v>25.67</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6965</v>
+        <v>0.6963</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21.48</v>
+        <v>21.49</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4278</v>
+        <v>0.4277</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.51</v>
+        <v>27.5</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32.03</v>
+        <v>32.02</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7921</v>
+        <v>0.7919</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1222,7 @@
         <v>31.29</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7857</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.73</v>
+        <v>31.74</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8153</v>
+        <v>0.8154</v>
       </c>
     </row>
     <row r="63">
@@ -1248,7 +1248,7 @@
         <v>29.04</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7941</v>
+        <v>0.7942</v>
       </c>
     </row>
     <row r="64">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.37</v>
+        <v>24.36</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6738</v>
+        <v>0.6737</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         <v>26.06</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6221</v>
+        <v>0.6219</v>
       </c>
     </row>
     <row r="67">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.36</v>
+        <v>28.35</v>
       </c>
       <c r="C67" t="n">
         <v>0.794</v>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>39.81</v>
+        <v>39.78</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9808</v>
+        <v>0.9807</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.04</v>
+        <v>21.05</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5804</v>
+        <v>0.5809</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.8</v>
+        <v>22.79</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6529</v>
+        <v>0.6526999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.56</v>
+        <v>30.54</v>
       </c>
       <c r="C72" t="n">
         <v>0.8206</v>
@@ -1378,7 +1378,7 @@
         <v>25.5</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5977</v>
+        <v>0.5975</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         <v>27.22</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6057</v>
+        <v>0.6056</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.31</v>
+        <v>26.32</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6965</v>
+        <v>0.6966</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.16</v>
+        <v>24.17</v>
       </c>
       <c r="C76" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="77">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.72</v>
+        <v>30.73</v>
       </c>
       <c r="C77" t="n">
         <v>0.7852</v>
@@ -1443,7 +1443,7 @@
         <v>23.67</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4794</v>
+        <v>0.4796</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         <v>29.81</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8119</v>
+        <v>0.8118</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.84</v>
+        <v>32.81</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9534</v>
+        <v>0.9533</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.77</v>
+        <v>29.76</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8189</v>
+        <v>0.8188</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.82</v>
+        <v>35.8</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9395</v>
+        <v>0.9394</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.58</v>
+        <v>28.59</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7207</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.3</v>
+        <v>22.29</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5327</v>
+        <v>0.5324</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>21.03</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6088</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.72</v>
+        <v>25.71</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7932</v>
+        <v>0.7927999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -1560,7 +1560,7 @@
         <v>25.04</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6024</v>
+        <v>0.6027</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1573,7 @@
         <v>27.39</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6957</v>
+        <v>0.6955</v>
       </c>
     </row>
     <row r="89">
@@ -1599,7 +1599,7 @@
         <v>27.24</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5603</v>
+        <v>0.5602</v>
       </c>
     </row>
     <row r="91">
@@ -1612,7 +1612,7 @@
         <v>25.11</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6461</v>
+        <v>0.6463</v>
       </c>
     </row>
     <row r="92">
@@ -1625,7 +1625,7 @@
         <v>29.14</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7144</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.68</v>
+        <v>26.69</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7564</v>
+        <v>0.7567</v>
       </c>
     </row>
     <row r="94">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.88</v>
+        <v>30.84</v>
       </c>
       <c r="C94" t="n">
         <v>0.8787</v>
@@ -1664,7 +1664,7 @@
         <v>26.05</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7187</v>
+        <v>0.7189</v>
       </c>
     </row>
     <row r="96">
@@ -1677,7 +1677,7 @@
         <v>26.02</v>
       </c>
       <c r="C96" t="n">
-        <v>0.7992</v>
+        <v>0.7995</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         <v>21.92</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3194</v>
+        <v>0.3193</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>27.06</v>
+        <v>27.05</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5626</v>
+        <v>0.5624</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.3</v>
+        <v>26.31</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7798</v>
+        <v>0.7799</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.92</v>
+        <v>26.91</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7365</v>
+        <v>0.7361</v>
       </c>
     </row>
     <row r="101">
@@ -1742,7 +1742,7 @@
         <v>25.1</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7298</v>
+        <v>0.7297</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.59</v>
+        <v>27.58</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7373</v>
+        <v>0.7372</v>
       </c>
     </row>
   </sheetData>
